--- a/newExported/comparison/au4_5_7_summary.xlsx
+++ b/newExported/comparison/au4_5_7_summary.xlsx
@@ -573,281 +573,281 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Obama 2012</t>
+          <t>Romney 2012</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13873</v>
+        <v>12859</v>
       </c>
       <c r="C6" t="n">
-        <v>0.158697469905572</v>
+        <v>0.16281203826114</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2985793162288219</v>
+        <v>0.2704828984301407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0921040870756145</v>
+        <v>0.08199704487129637</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2144770943430937</v>
+        <v>0.193462952058614</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5935111367404311</v>
+        <v>0.5543860331285482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.505942674279941</v>
+        <v>0.598054607115087</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romney 2012</t>
+          <t>Obama 2012</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12859</v>
+        <v>13873</v>
       </c>
       <c r="C7" t="n">
-        <v>0.16281203826114</v>
+        <v>0.158697469905572</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2704828984301407</v>
+        <v>0.2985793162288219</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08199704487129637</v>
+        <v>0.0921040870756145</v>
       </c>
       <c r="F7" t="n">
-        <v>0.193462952058614</v>
+        <v>0.2144770943430937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5543860331285482</v>
+        <v>0.5935111367404311</v>
       </c>
       <c r="H7" t="n">
-        <v>0.598054607115087</v>
+        <v>0.505942674279941</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clinton 2016</t>
+          <t>Trump 2016</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15988</v>
+        <v>15814</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04965286464848637</v>
+        <v>0.3052870873909194</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1542656284409169</v>
+        <v>0.4209946008795409</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08027520640480361</v>
+        <v>0.07309725559630707</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1964251712030383</v>
+        <v>0.1571486944336527</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4354315736802602</v>
+        <v>0.5825085367395979</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4696658613058194</v>
+        <v>0.400058079824044</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trump 2016</t>
+          <t>Clinton 2016</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15814</v>
+        <v>15988</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3052870873909194</v>
+        <v>0.04965286464848637</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4209946008795409</v>
+        <v>0.1542656284409169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07309725559630707</v>
+        <v>0.08027520640480361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1571486944336527</v>
+        <v>0.1964251712030383</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5825085367395979</v>
+        <v>0.4354315736802602</v>
       </c>
       <c r="H9" t="n">
-        <v>0.400058079824044</v>
+        <v>0.4696658613058194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Biden 2020</t>
+          <t>Trump 2020</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12022</v>
+        <v>13148</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9303244052570289</v>
+        <v>0.7562298448433221</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5982426872550386</v>
+        <v>0.4877550753916471</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09504824488437864</v>
+        <v>0.1280544569516276</v>
       </c>
       <c r="F10" t="n">
-        <v>0.246853777481288</v>
+        <v>0.3208229455084354</v>
       </c>
       <c r="G10" t="n">
-        <v>1.307759108301447</v>
+        <v>0.8998113781563737</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8463434089213493</v>
+        <v>0.4780672572379097</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Trump 2020</t>
+          <t>Biden 2020</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13148</v>
+        <v>12022</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7562298448433221</v>
+        <v>0.9303244052570289</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4877550753916471</v>
+        <v>0.5982426872550386</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1280544569516276</v>
+        <v>0.09504824488437864</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3208229455084354</v>
+        <v>0.246853777481288</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8998113781563737</v>
+        <v>1.307759108301447</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4780672572379097</v>
+        <v>0.8463434089213493</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biden 2024b</t>
+          <t>Trump 2024 (1st)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9732</v>
+        <v>12414</v>
       </c>
       <c r="C12" t="n">
-        <v>1.009190300041102</v>
+        <v>1.235264217818592</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5687995406427874</v>
+        <v>0.4606378859938182</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1396228935470612</v>
+        <v>0.06256806830997261</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3667564008023236</v>
+        <v>0.1628777621091797</v>
       </c>
       <c r="G12" t="n">
-        <v>1.909169749280724</v>
+        <v>0.6613041727082327</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8050335870696093</v>
+        <v>0.3841102157114453</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Harris 2024</t>
+          <t>Biden 2024</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11848</v>
+        <v>9732</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2499898717083052</v>
+        <v>1.009190300041102</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3633381615415081</v>
+        <v>0.5687995406427874</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1610946995273464</v>
+        <v>0.1396228935470612</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4142404861452762</v>
+        <v>0.3667564008023236</v>
       </c>
       <c r="G13" t="n">
-        <v>1.082966745442269</v>
+        <v>1.909169749280724</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6463007446704948</v>
+        <v>0.8050335870696093</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trump 2024b</t>
+          <t>Trump 2024 (2nd)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12414</v>
+        <v>13315</v>
       </c>
       <c r="C14" t="n">
-        <v>1.235264217818592</v>
+        <v>1.626488171235449</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4606378859938182</v>
+        <v>0.4420583916949674</v>
       </c>
       <c r="E14" t="n">
-        <v>0.06256806830997261</v>
+        <v>0.09006458880961322</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1628777621091797</v>
+        <v>0.2239408574156822</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6613041727082327</v>
+        <v>0.12733308298911</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3841102157114453</v>
+        <v>0.1988497034946535</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trump 2024</t>
+          <t>Harris 2024</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13315</v>
+        <v>11848</v>
       </c>
       <c r="C15" t="n">
-        <v>1.626488171235449</v>
+        <v>0.2499898717083052</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4420583916949674</v>
+        <v>0.3633381615415081</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09006458880961322</v>
+        <v>0.1610946995273464</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2239408574156822</v>
+        <v>0.4142404861452762</v>
       </c>
       <c r="G15" t="n">
-        <v>0.12733308298911</v>
+        <v>1.082966745442269</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1988497034946535</v>
+        <v>0.6463007446704948</v>
       </c>
     </row>
   </sheetData>
